--- a/qc/SDTM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/SDTM-PROGRAMMING-TRACKER.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-02: cm.parquet does not include post-trial anti-cancer therapy (only supportive-care meds). Affects T-DS-03 + T-EFF-12. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q3" s="17" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-03: SDTM.DS does not carry explicit DSCAT='PROTOCOL DEVIATION' records; only PPROTFL='N' is derivable. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q7" s="17" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-11: relrec.parquet contains duplicate rows (~5 per multi-visit lesion) because relrec.R emits one row per TU/TR record rather than one per unique lesion-id. compare_sdtm.R falls back to identical() comparison. Future relrec.R revision should distinct() on (USUBJID, RDOMAIN, IDVARVAL). Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q12" s="17" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="P19" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-01: SUPPSU is a legacy artifact (STUDYID 'TORIVUMAB-NSCLC-301', not 'CTX-NSCLC-301'); no generator script in programs/sdtm/. See SDTM-MAPPING-SPEC.md §17. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q19" s="17" t="inlineStr">

--- a/qc/SDTM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/SDTM-PROGRAMMING-TRACKER.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K3" s="17" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K4" s="17" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K10" s="17" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K11" s="17" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K13" s="17" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="K22" s="18" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Generated 2026-05-16 — synthetic data, not for regulatory submission</t>
+          <t>Generated 2026-05-17 — synthetic data, not for regulatory submission</t>
         </is>
       </c>
       <c r="B2" s="16"/>

--- a/qc/SDTM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/SDTM-PROGRAMMING-TRACKER.xlsx
@@ -520,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t>AL-02: cm.parquet does not include post-trial anti-cancer therapy (only supportive-care meds). Affects T-DS-03 + T-EFF-12. Accepted — not a defect.</t>
+          <t>AL-02 (partial): cm.parquet still does not include post-trial anti-cancer therapy (only supportive-care meds). Affects T-EFF-12 OSWOT (uses only TRTEDT+30d component). Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q3" s="17" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t>AL-03: SDTM.DS does not carry explicit DSCAT='PROTOCOL DEVIATION' records; only PPROTFL='N' is derivable. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="Q7" s="17" t="inlineStr">
@@ -1211,41 +1211,41 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Interventions</t>
+          <t>Special purpose</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>raw/exposure.csv</t>
+          <t>raw/protocol_deviations.csv</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/ex.R</t>
+          <t>programs/sdtm/dv.R</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §3</t>
+          <t>SDTM-MAPPING-SPEC.md §22</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/ex.parquet</t>
+          <t>datasets/sdtm/dv.parquet</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>13,403</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H8" s="17">
-        <v>80.7</v>
+        <v>13.1</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -1306,41 +1306,41 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Interventions</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>raw/labs.csv</t>
+          <t>raw/exposure.csv</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/lb.R</t>
+          <t>programs/sdtm/ex.R</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §10</t>
+          <t>SDTM-MAPPING-SPEC.md §3</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/lb.parquet</t>
+          <t>datasets/sdtm/ex.parquet</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>122,601</t>
+          <t>13,403</t>
         </is>
       </c>
       <c r="H9" s="17">
-        <v>706.1</v>
+        <v>80.7</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>raw/medical_history.csv</t>
+          <t>raw/labs.csv</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/mh.R</t>
+          <t>programs/sdtm/lb.R</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §7</t>
+          <t>SDTM-MAPPING-SPEC.md §10</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/mh.parquet</t>
+          <t>datasets/sdtm/lb.parquet</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>2,061</t>
+          <t>122,601</t>
         </is>
       </c>
       <c r="H10" s="17">
-        <v>25.7</v>
+        <v>706.1</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -1496,41 +1496,41 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>raw/physical_exam.csv</t>
+          <t>raw/medical_history.csv</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/pe.R</t>
+          <t>programs/sdtm/mh.R</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §12</t>
+          <t>SDTM-MAPPING-SPEC.md §7</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/pe.parquet</t>
+          <t>datasets/sdtm/mh.parquet</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>25,596</t>
+          <t>2,061</t>
         </is>
       </c>
       <c r="H11" s="17">
-        <v>67.2</v>
+        <v>25.7</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -1591,41 +1591,41 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>RELREC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>tu.parquet + tr.parquet + rs.parquet</t>
+          <t>raw/physical_exam.csv</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/relrec.R</t>
+          <t>programs/sdtm/pe.R</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §21</t>
+          <t>SDTM-MAPPING-SPEC.md §12</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/relrec.parquet</t>
+          <t>datasets/sdtm/pe.parquet</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>21,162</t>
+          <t>25,596</t>
         </is>
       </c>
       <c r="H12" s="17">
-        <v>60.2</v>
+        <v>67.2</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>AL-11: relrec.parquet contains duplicate rows (~5 per multi-visit lesion) because relrec.R emits one row per TU/TR record rather than one per unique lesion-id. compare_sdtm.R falls back to identical() comparison. Future relrec.R revision should distinct() on (USUBJID, RDOMAIN, IDVARVAL). Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="Q12" s="17" t="inlineStr">
@@ -1686,41 +1686,41 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RELREC</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>raw/overall_response.csv</t>
+          <t>tu.parquet + tr.parquet + rs.parquet</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/rs.R</t>
+          <t>programs/sdtm/relrec.R</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §15</t>
+          <t>SDTM-MAPPING-SPEC.md §21</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/rs.parquet</t>
+          <t>datasets/sdtm/relrec.parquet</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>2,762</t>
+          <t>21,162</t>
         </is>
       </c>
       <c r="H13" s="17">
-        <v>25.7</v>
+        <v>60.2</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-11: relrec.parquet contains duplicate rows (~5 per multi-visit lesion) because relrec.R emits one row per TU/TR record rather than one per unique lesion-id. compare_sdtm.R falls back to identical() comparison. Future relrec.R revision should distinct() on (USUBJID, RDOMAIN, IDVARVAL). Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q13" s="17" t="inlineStr">
@@ -1781,41 +1781,41 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Interventions</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>raw/substance_use.csv</t>
+          <t>raw/overall_response.csv</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/su.R</t>
+          <t>programs/sdtm/rs.R</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §8</t>
+          <t>SDTM-MAPPING-SPEC.md §15</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/su.parquet</t>
+          <t>datasets/sdtm/rs.parquet</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>1,217</t>
+          <t>2,762</t>
         </is>
       </c>
       <c r="H14" s="17">
-        <v>14.7</v>
+        <v>25.7</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1876,41 +1876,41 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>SUPPAE</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Interventions</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>ae.parquet + raw/adverse_events.csv</t>
+          <t>raw/substance_use.csv</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/suppae.R</t>
+          <t>programs/sdtm/su.R</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §18</t>
+          <t>SDTM-MAPPING-SPEC.md §8</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/suppae.parquet</t>
+          <t>datasets/sdtm/su.parquet</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>8,523</t>
+          <t>1,217</t>
         </is>
       </c>
       <c r="H15" s="17">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>SUPPCM</t>
+          <t>SUPPAE</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -1981,31 +1981,31 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>cm.parquet</t>
+          <t>ae.parquet + raw/adverse_events.csv</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/suppcm.R</t>
+          <t>programs/sdtm/suppae.R</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §19</t>
+          <t>SDTM-MAPPING-SPEC.md §18</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/suppcm.parquet</t>
+          <t>datasets/sdtm/suppae.parquet</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>4,394</t>
+          <t>8,523</t>
         </is>
       </c>
       <c r="H16" s="17">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>SUPPCM</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -2076,31 +2076,31 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>raw/demographics.csv</t>
+          <t>cm.parquet</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/suppdm.R</t>
+          <t>programs/sdtm/suppcm.R</t>
         </is>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §16</t>
+          <t>SDTM-MAPPING-SPEC.md §19</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/suppdm.parquet</t>
+          <t>datasets/sdtm/suppcm.parquet</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>1,799</t>
+          <t>4,394</t>
         </is>
       </c>
       <c r="H17" s="17">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>SUPPLB</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -2171,31 +2171,31 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>lb.parquet</t>
+          <t>raw/demographics.csv</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/supplb.R</t>
+          <t>programs/sdtm/suppdm.R</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §20</t>
+          <t>SDTM-MAPPING-SPEC.md §16</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/supplb.parquet</t>
+          <t>datasets/sdtm/suppdm.parquet</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>245,202</t>
+          <t>1,799</t>
         </is>
       </c>
       <c r="H18" s="17">
-        <v>108.3</v>
+        <v>15.1</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>SUPPSU</t>
+          <t>SUPPLB</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -2266,31 +2266,31 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>raw/substance_use.csv (legacy)</t>
+          <t>lb.parquet</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>(generator missing — see spec §17)</t>
+          <t>programs/sdtm/supplb.R</t>
         </is>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §17</t>
+          <t>SDTM-MAPPING-SPEC.md §20</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/suppsu.parquet</t>
+          <t>datasets/sdtm/supplb.parquet</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>245,202</t>
         </is>
       </c>
       <c r="H19" s="17">
-        <v>9.8</v>
+        <v>108.3</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="P19" s="17" t="inlineStr">
         <is>
-          <t>AL-01: SUPPSU is a legacy artifact (STUDYID 'TORIVUMAB-NSCLC-301', not 'CTX-NSCLC-301'); no generator script in programs/sdtm/. See SDTM-MAPPING-SPEC.md §17. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="Q19" s="17" t="inlineStr">
@@ -2351,41 +2351,41 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SUPPSU</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>raw/tumor_measurements.csv</t>
+          <t>raw/substance_use.csv (legacy)</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>programs/sdtm/tr.R</t>
+          <t>(generator missing — see spec §17)</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>SDTM-MAPPING-SPEC.md §14</t>
+          <t>SDTM-MAPPING-SPEC.md §17</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>datasets/sdtm/tr.parquet</t>
+          <t>datasets/sdtm/suppsu.parquet</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>9,200</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H20" s="17">
-        <v>80.3</v>
+        <v>9.8</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="P20" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-01: SUPPSU is a legacy artifact (STUDYID 'TORIVUMAB-NSCLC-301', not 'CTX-NSCLC-301'); no generator script in programs/sdtm/. See SDTM-MAPPING-SPEC.md §17. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="Q20" s="17" t="inlineStr">
@@ -2446,231 +2446,326 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>raw/tumor_measurements.csv</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>programs/sdtm/tr.R</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>SDTM-MAPPING-SPEC.md §14</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>datasets/sdtm/tr.parquet</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="H21" s="17">
+        <v>80.3</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming</t>
+        </is>
+      </c>
+      <c r="M21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="P21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>raw/tumor_measurements.csv</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>programs/sdtm/tu.R</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>SDTM-MAPPING-SPEC.md §13</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>datasets/sdtm/tu.parquet</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>9,148</t>
         </is>
       </c>
-      <c r="H21" s="17">
+      <c r="H22" s="17">
         <v>46</v>
       </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" s="17" t="inlineStr">
         <is>
           <t>Independent double programming</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" s="17" t="inlineStr">
         <is>
           <t>Programmed — pending QC</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R21" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S21" s="20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="P22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>VS</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>raw/vital_signs.csv</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>programs/sdtm/vs.R</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>SDTM-MAPPING-SPEC.md §11</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>datasets/sdtm/vs.parquet</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>52,864</t>
         </is>
       </c>
-      <c r="H22" s="18">
+      <c r="H23" s="18">
         <v>307.2</v>
       </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
         <is>
           <t>Independent double programming</t>
         </is>
       </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" s="18" t="inlineStr">
         <is>
           <t>Programmed — pending QC</t>
         </is>
       </c>
-      <c r="P22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S22" s="21" t="inlineStr">
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S23" s="21" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Programmed — pending QC">
       <formula>NOT(ISERROR(SEARCH("Programmed — pending QC", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="QC in progress">
       <formula>NOT(ISERROR(SEARCH("QC in progress", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="QC passed — issues none">
       <formula>NOT(ISERROR(SEARCH("QC passed — issues none", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="QC passed — minor issues resolved">
       <formula>NOT(ISERROR(SEARCH("QC passed — minor issues resolved", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="QC failed — under rework">
       <formula>NOT(ISERROR(SEARCH("QC failed — under rework", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Locked">
       <formula>NOT(ISERROR(SEARCH("Locked", O2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="O2:O22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="O2:O23">
       <formula1>"Not started,Programmed — pending QC,QC in progress,QC passed — issues none,QC passed — minor issues resolved,QC failed — under rework,Locked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/qc/SDTM-PROGRAMMING-TRACKER.xlsx
+++ b/qc/SDTM-PROGRAMMING-TRACKER.xlsx
@@ -766,11 +766,11 @@
       </c>
       <c r="G3" s="17" t="inlineStr">
         <is>
-          <t>2,197</t>
+          <t>2,330</t>
         </is>
       </c>
       <c r="H3" s="17">
-        <v>31.7</v>
+        <v>33.5</v>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t>AL-02 (partial): cm.parquet still does not include post-trial anti-cancer therapy (only supportive-care meds). Affects T-EFF-12 OSWOT (uses only TRTEDT+30d component). Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="Q3" s="17" t="inlineStr">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>25,596</t>
+          <t>25,590</t>
         </is>
       </c>
       <c r="H12" s="17">
-        <v>67.2</v>
+        <v>66.3</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -1716,11 +1716,11 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>21,162</t>
+          <t>16,107</t>
         </is>
       </c>
       <c r="H13" s="17">
-        <v>60.2</v>
+        <v>54.8</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>2,762</t>
+          <t>5,524</t>
         </is>
       </c>
       <c r="H14" s="17">
-        <v>25.7</v>
+        <v>31.6</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>1,217</t>
+          <t>1,220</t>
         </is>
       </c>
       <c r="H15" s="17">
@@ -2096,11 +2096,11 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>4,394</t>
+          <t>4,527</t>
         </is>
       </c>
       <c r="H17" s="17">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="H20" s="17">
-        <v>9.8</v>
+        <v>7</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
